--- a/Result/profitability/3632.xlsx
+++ b/Result/profitability/3632.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>4.27</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4687499999999999</v>
+        <v>0.4412499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>57.66875</v>
+        <v>56.75125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.32</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6287499999999999</v>
+        <v>0.63625</v>
       </c>
       <c r="N3" t="n">
-        <v>59.57875</v>
+        <v>59.38875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6975</v>
+        <v>0.6849999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>62.17875</v>
+        <v>61.91</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.18</v>
       </c>
       <c r="M5" t="n">
-        <v>0.73</v>
+        <v>0.73125</v>
       </c>
       <c r="N5" t="n">
-        <v>64.37375</v>
+        <v>63.655</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8812499999999999</v>
+        <v>0.8787499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>64.17999999999999</v>
+        <v>63.72375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.87</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>0.98125</v>
       </c>
       <c r="N7" t="n">
-        <v>64.86</v>
+        <v>64.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07875</v>
+        <v>1.04875</v>
       </c>
       <c r="N8" t="n">
-        <v>64.9725</v>
+        <v>63.7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -1645,7 +1645,7 @@
         <v>0.92</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7799999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="N10" t="n">
         <v>62.31</v>
@@ -1899,7 +1899,7 @@
         <v>0.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>55.53125</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3632</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>70</v>
+      </c>
+      <c r="D75" t="n">
+        <v>34</v>
+      </c>
+      <c r="E75" t="n">
+        <v>36</v>
+      </c>
+      <c r="F75" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-11.41%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.08749999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>55.89375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-10.18</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.164485377282275</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.05263157894736847</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1000696136442742</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
